--- a/docentes/Velasco Sánchez David - Estadisticos 20211.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
   <si>
     <t>Mat</t>
   </si>
@@ -82,40 +82,103 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ARROYO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TERRAZAS</t>
   </si>
   <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ROSALES</t>
+    <t>LUIS REY</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>CITLALLI</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEXIS</t>
   </si>
   <si>
     <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
-    <t>ISRAEL</t>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>MARIA REYNA</t>
   </si>
   <si>
     <t>SINAI ANTONIO</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -965,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,94 +1060,255 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920162</v>
+        <v>21330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920284</v>
+        <v>21330051920213</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920207</v>
+        <v>20330051920093</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920213</v>
+        <v>20330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920285</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920152</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920162</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920165</v>
+      </c>
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920175</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920180</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920207</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
-        <v>6</v>
+      <c r="G12">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20211.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -82,103 +82,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>ARROYO</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>CASTAÑEDA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
+    <t>PAUL ARAVIER</t>
   </si>
   <si>
     <t>CITLALLI</t>
   </si>
   <si>
-    <t>CRISTIAN ALEXIS</t>
-  </si>
-  <si>
     <t>CRISTIAN FERNANDO</t>
   </si>
   <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
     <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>MARIA REYNA</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -631,16 +568,16 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -657,16 +594,16 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5">
         <v>7.1</v>
@@ -748,16 +685,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.34999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -771,16 +711,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>74.19</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -794,16 +737,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -817,16 +763,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -840,16 +789,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>57.58</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -905,16 +857,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>70.59</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -931,16 +883,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>67.73999999999999</v>
+        <v>74.19</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -954,19 +906,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -980,19 +932,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>68.56999999999999</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1009,16 +961,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>63.64</v>
+        <v>57.58</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1060,255 +1012,94 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920212</v>
+        <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920213</v>
+        <v>20330051920285</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920093</v>
+        <v>21330051920162</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920284</v>
+        <v>21330051920175</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920285</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920152</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920162</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920165</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920175</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
         <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920180</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920207</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20211.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,40 +82,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>JUAN GERARDO</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
   </si>
   <si>
     <t>JHOSUA LEVY</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
 </sst>
 </file>
@@ -539,19 +566,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>21</v>
       </c>
       <c r="G3">
-        <v>67.73999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="H3">
         <v>7.3</v>
@@ -708,19 +735,19 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3">
         <v>23</v>
       </c>
       <c r="G3">
-        <v>74.19</v>
+        <v>71.88</v>
       </c>
       <c r="H3">
         <v>7.3</v>
@@ -857,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -877,22 +904,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>74.19</v>
+        <v>81.25</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -909,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -935,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>71.43000000000001</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -961,16 +988,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>57.58</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -980,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,45 +1039,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>21330051920156</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920285</v>
+        <v>21330051920164</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1058,16 +1085,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920162</v>
+        <v>21330051920166</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1076,30 +1103,99 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920175</v>
+        <v>21330051920202</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920307</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920175</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>3</v>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920188</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
